--- a/main/ig/StructureDefinition-fr-lm-attachment.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-attachment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-attachment.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-attachment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-attachment.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-attachment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-attachment.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-attachment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-attachment.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-attachment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-attachment.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-attachment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-attachment.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-attachment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-attachment.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-attachment.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="159">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -452,6 +452,9 @@
   </si>
   <si>
     <t>Type MIME de la piece jointe, avec encodage de caracteres, etc.</t>
+  </si>
+  <si>
+    <t>preferred</t>
   </si>
   <si>
     <t>(preferred): BCP-13</t>
@@ -2816,10 +2819,10 @@
         <v>73</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>73</v>
+        <v>142</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Z20" t="s" s="2">
         <v>73</v>
@@ -2857,10 +2860,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2886,10 +2889,10 @@
         <v>131</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2916,10 +2919,10 @@
         <v>73</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>73</v>
+        <v>142</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Z21" t="s" s="2">
         <v>73</v>
@@ -2940,7 +2943,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -2957,10 +2960,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2983,13 +2986,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3040,7 +3043,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3057,10 +3060,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3083,13 +3086,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3140,7 +3143,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3157,10 +3160,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3183,13 +3186,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3240,7 +3243,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3257,10 +3260,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3283,13 +3286,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3340,7 +3343,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
